--- a/data/processed/positivacao/2020-07_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2020-07_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -23879,7 +23879,7 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B906" t="inlineStr"/>
@@ -35101,7 +35101,7 @@
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1338" t="inlineStr"/>
@@ -64123,7 +64123,7 @@
     <row r="2455">
       <c r="A2455" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2455" t="inlineStr"/>
@@ -65820,12 +65820,12 @@
       <c r="A2521" t="inlineStr"/>
       <c r="B2521" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 0 cliente(s), não positivou 89 cliente(s) - Total vendido: R$ 0,00
+          <t>Vendedor 1 - VENDEDOR 01: positivou 0 cliente(s), não positivou 89 cliente(s) - Total vendido: R$ 0,00
 Vendedor 18 - LOJA: positivou 16 cliente(s), não positivou 791 cliente(s) - Total vendido: R$ 7.783,56
-Vendedor 3 - FERNANDA: positivou 7 cliente(s), não positivou 424 cliente(s) - Total vendido: R$ 7.944,59
-Vendedor 4 - DANIELA: positivou 0 cliente(s), não positivou 656 cliente(s) - Total vendido: R$ 0,00
+Vendedor 3 - VENDEDOR 03: positivou 7 cliente(s), não positivou 424 cliente(s) - Total vendido: R$ 7.944,59
+Vendedor 4 - VENDEDOR 04: positivou 0 cliente(s), não positivou 656 cliente(s) - Total vendido: R$ 0,00
 Vendedor 5 - SITE: positivou 8 cliente(s), não positivou 451 cliente(s) - Total vendido: R$ 973,09
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 64 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 64 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2521" t="inlineStr"/>
